--- a/inventory/مستحقات جرد الصيدليات 2026.xlsx
+++ b/inventory/مستحقات جرد الصيدليات 2026.xlsx
@@ -731,12 +731,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>الأحد</t>
+          <t>الاثنين</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -774,12 +774,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>الأحد</t>
+          <t>الاثنين</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -813,12 +813,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>الأحد</t>
+          <t>الاثنين</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -852,12 +852,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>الأحد</t>
+          <t>الاثنين</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">

--- a/inventory/مستحقات جرد الصيدليات 2026.xlsx
+++ b/inventory/مستحقات جرد الصيدليات 2026.xlsx
@@ -10,7 +10,7 @@
     <sheet name="السجل" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'السجل'!$A$1:$I$179</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'السجل'!$A$1:$I$178</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -468,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I180"/>
+  <dimension ref="A1:I179"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5709,7 +5709,7 @@
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>د. محمد جمال</t>
+          <t>د. حسام شلش</t>
         </is>
       </c>
       <c r="F131" s="2" t="inlineStr"/>
@@ -5744,14 +5744,18 @@
         </is>
       </c>
       <c r="D132" s="2" t="n">
-        <v>8</v>
+        <v>60</v>
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>د. حسام شلش</t>
-        </is>
-      </c>
-      <c r="F132" s="2" t="inlineStr"/>
+          <t>د. علي خليفة</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
           <t>نعم</t>
@@ -5759,11 +5763,11 @@
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
-          <t>مراجعة فقط</t>
+          <t>جرد + مراجعة</t>
         </is>
       </c>
       <c r="I132" s="3" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
     </row>
     <row r="133">
@@ -5787,14 +5791,10 @@
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>د. علي خليفة</t>
-        </is>
-      </c>
-      <c r="F133" s="2" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
-      </c>
+          <t>د. السيد حسن</t>
+        </is>
+      </c>
+      <c r="F133" s="2" t="inlineStr"/>
       <c r="G133" s="2" t="inlineStr">
         <is>
           <t>نعم</t>
@@ -5802,11 +5802,11 @@
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
-          <t>جرد + مراجعة</t>
+          <t>مراجعة فقط</t>
         </is>
       </c>
       <c r="I133" s="3" t="n">
-        <v>200</v>
+        <v>150</v>
       </c>
     </row>
     <row r="134">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>د. السيد حسن</t>
+          <t>د. حسام شلش</t>
         </is>
       </c>
       <c r="F134" s="2" t="inlineStr"/>
@@ -5851,12 +5851,12 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>الثلاثاء</t>
+          <t>الأربعاء</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
@@ -5865,14 +5865,18 @@
         </is>
       </c>
       <c r="D135" s="2" t="n">
-        <v>60</v>
+        <v>24</v>
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>د. محمد جمال</t>
-        </is>
-      </c>
-      <c r="F135" s="2" t="inlineStr"/>
+          <t>د. حسام شلش</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
           <t>نعم</t>
@@ -5880,22 +5884,22 @@
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
-          <t>مراجعة فقط</t>
+          <t>جرد + مراجعة</t>
         </is>
       </c>
       <c r="I135" s="3" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>الثلاثاء</t>
+          <t>الأربعاء</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
@@ -5904,11 +5908,11 @@
         </is>
       </c>
       <c r="D136" s="2" t="n">
-        <v>60</v>
+        <v>24</v>
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>د. حسام شلش</t>
+          <t>د. علي خليفة</t>
         </is>
       </c>
       <c r="F136" s="2" t="inlineStr"/>
@@ -5947,14 +5951,10 @@
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>د. حسام شلش</t>
-        </is>
-      </c>
-      <c r="F137" s="2" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
-      </c>
+          <t>د. السيد حسن</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="inlineStr"/>
       <c r="G137" s="2" t="inlineStr">
         <is>
           <t>نعم</t>
@@ -5962,11 +5962,11 @@
       </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
-          <t>جرد + مراجعة</t>
+          <t>مراجعة فقط</t>
         </is>
       </c>
       <c r="I137" s="3" t="n">
-        <v>200</v>
+        <v>150</v>
       </c>
     </row>
     <row r="138">
@@ -5986,14 +5986,18 @@
         </is>
       </c>
       <c r="D138" s="2" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>د. علي خليفة</t>
-        </is>
-      </c>
-      <c r="F138" s="2" t="inlineStr"/>
+          <t>د. حسام شلش</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
           <t>نعم</t>
@@ -6001,11 +6005,11 @@
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
-          <t>مراجعة فقط</t>
+          <t>جرد + مراجعة</t>
         </is>
       </c>
       <c r="I138" s="3" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
     </row>
     <row r="139">
@@ -6025,11 +6029,11 @@
         </is>
       </c>
       <c r="D139" s="2" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>د. السيد حسن</t>
+          <t>د. علي خليفة</t>
         </is>
       </c>
       <c r="F139" s="2" t="inlineStr"/>
@@ -6068,14 +6072,10 @@
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>د. حسام شلش</t>
-        </is>
-      </c>
-      <c r="F140" s="2" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
-      </c>
+          <t>د. السيد حسن</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr"/>
       <c r="G140" s="2" t="inlineStr">
         <is>
           <t>نعم</t>
@@ -6083,22 +6083,22 @@
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
-          <t>جرد + مراجعة</t>
+          <t>مراجعة فقط</t>
         </is>
       </c>
       <c r="I140" s="3" t="n">
-        <v>200</v>
+        <v>150</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>الأربعاء</t>
+          <t>الخميس</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
@@ -6107,14 +6107,18 @@
         </is>
       </c>
       <c r="D141" s="2" t="n">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
           <t>د. علي خليفة</t>
         </is>
       </c>
-      <c r="F141" s="2" t="inlineStr"/>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
           <t>نعم</t>
@@ -6122,22 +6126,22 @@
       </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
-          <t>مراجعة فقط</t>
+          <t>جرد + مراجعة</t>
         </is>
       </c>
       <c r="I141" s="3" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>الأربعاء</t>
+          <t>الخميس</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
@@ -6146,11 +6150,11 @@
         </is>
       </c>
       <c r="D142" s="2" t="n">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>د. السيد حسن</t>
+          <t>د. حسام شلش</t>
         </is>
       </c>
       <c r="F142" s="2" t="inlineStr"/>
@@ -6189,14 +6193,10 @@
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>د. علي خليفة</t>
-        </is>
-      </c>
-      <c r="F143" s="2" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
-      </c>
+          <t>د. السيد حسن</t>
+        </is>
+      </c>
+      <c r="F143" s="2" t="inlineStr"/>
       <c r="G143" s="2" t="inlineStr">
         <is>
           <t>نعم</t>
@@ -6204,11 +6204,11 @@
       </c>
       <c r="H143" s="2" t="inlineStr">
         <is>
-          <t>جرد + مراجعة</t>
+          <t>مراجعة فقط</t>
         </is>
       </c>
       <c r="I143" s="3" t="n">
-        <v>200</v>
+        <v>150</v>
       </c>
     </row>
     <row r="144">
@@ -6228,14 +6228,18 @@
         </is>
       </c>
       <c r="D144" s="2" t="n">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>د. حسام شلش</t>
-        </is>
-      </c>
-      <c r="F144" s="2" t="inlineStr"/>
+          <t>د. علي خليفة</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
           <t>نعم</t>
@@ -6243,11 +6247,11 @@
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
-          <t>مراجعة فقط</t>
+          <t>جرد + مراجعة</t>
         </is>
       </c>
       <c r="I144" s="3" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
     </row>
     <row r="145">
@@ -6267,11 +6271,11 @@
         </is>
       </c>
       <c r="D145" s="2" t="n">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>د. السيد حسن</t>
+          <t>د. حسام شلش</t>
         </is>
       </c>
       <c r="F145" s="2" t="inlineStr"/>
@@ -6310,14 +6314,10 @@
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>د. علي خليفة</t>
-        </is>
-      </c>
-      <c r="F146" s="2" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
-      </c>
+          <t>د. السيد حسن</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="inlineStr"/>
       <c r="G146" s="2" t="inlineStr">
         <is>
           <t>نعم</t>
@@ -6325,22 +6325,22 @@
       </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
-          <t>جرد + مراجعة</t>
+          <t>مراجعة فقط</t>
         </is>
       </c>
       <c r="I146" s="3" t="n">
-        <v>200</v>
+        <v>150</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>الخميس</t>
+          <t>الجمعة</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
@@ -6349,14 +6349,18 @@
         </is>
       </c>
       <c r="D147" s="2" t="n">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
           <t>د. حسام شلش</t>
         </is>
       </c>
-      <c r="F147" s="2" t="inlineStr"/>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
           <t>نعم</t>
@@ -6364,22 +6368,22 @@
       </c>
       <c r="H147" s="2" t="inlineStr">
         <is>
-          <t>مراجعة فقط</t>
+          <t>جرد + مراجعة</t>
         </is>
       </c>
       <c r="I147" s="3" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>الخميس</t>
+          <t>الجمعة</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
@@ -6388,11 +6392,11 @@
         </is>
       </c>
       <c r="D148" s="2" t="n">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>د. السيد حسن</t>
+          <t>د. علي خليفة</t>
         </is>
       </c>
       <c r="F148" s="2" t="inlineStr"/>
@@ -6431,14 +6435,10 @@
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>د. حسام شلش</t>
-        </is>
-      </c>
-      <c r="F149" s="2" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
-      </c>
+          <t>د. الحسن الغنيمي</t>
+        </is>
+      </c>
+      <c r="F149" s="2" t="inlineStr"/>
       <c r="G149" s="2" t="inlineStr">
         <is>
           <t>نعم</t>
@@ -6446,11 +6446,11 @@
       </c>
       <c r="H149" s="2" t="inlineStr">
         <is>
-          <t>جرد + مراجعة</t>
+          <t>مراجعة فقط</t>
         </is>
       </c>
       <c r="I149" s="3" t="n">
-        <v>200</v>
+        <v>150</v>
       </c>
     </row>
     <row r="150">
@@ -6474,7 +6474,7 @@
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>د. علي خليفة</t>
+          <t>د. محمد فؤاد</t>
         </is>
       </c>
       <c r="F150" s="2" t="inlineStr"/>
@@ -6513,7 +6513,7 @@
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>د. الحسن الغنيمي</t>
+          <t>د. أيمن حسين</t>
         </is>
       </c>
       <c r="F151" s="2" t="inlineStr"/>
@@ -6534,12 +6534,12 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>الجمعة</t>
+          <t>السبت</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
@@ -6548,14 +6548,18 @@
         </is>
       </c>
       <c r="D152" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>د. محمد فؤاد</t>
-        </is>
-      </c>
-      <c r="F152" s="2" t="inlineStr"/>
+          <t>د. علي خليفة</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
           <t>نعم</t>
@@ -6563,11 +6567,11 @@
       </c>
       <c r="H152" s="2" t="inlineStr">
         <is>
-          <t>مراجعة فقط</t>
+          <t>جرد + مراجعة</t>
         </is>
       </c>
       <c r="I152" s="3" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
     </row>
     <row r="153">
@@ -6591,14 +6595,10 @@
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>د. علي خليفة</t>
-        </is>
-      </c>
-      <c r="F153" s="2" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
-      </c>
+          <t>د. السيد حسن</t>
+        </is>
+      </c>
+      <c r="F153" s="2" t="inlineStr"/>
       <c r="G153" s="2" t="inlineStr">
         <is>
           <t>نعم</t>
@@ -6606,11 +6606,11 @@
       </c>
       <c r="H153" s="2" t="inlineStr">
         <is>
-          <t>جرد + مراجعة</t>
+          <t>مراجعة فقط</t>
         </is>
       </c>
       <c r="I153" s="3" t="n">
-        <v>200</v>
+        <v>150</v>
       </c>
     </row>
     <row r="154">
@@ -6634,7 +6634,7 @@
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>د. السيد حسن</t>
+          <t>د. حسام شلش</t>
         </is>
       </c>
       <c r="F154" s="2" t="inlineStr"/>
@@ -6655,12 +6655,12 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>السبت</t>
+          <t>الأحد</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
@@ -6669,14 +6669,18 @@
         </is>
       </c>
       <c r="D155" s="2" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
           <t>د. حسام شلش</t>
         </is>
       </c>
-      <c r="F155" s="2" t="inlineStr"/>
+      <c r="F155" s="2" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
           <t>نعم</t>
@@ -6684,11 +6688,11 @@
       </c>
       <c r="H155" s="2" t="inlineStr">
         <is>
-          <t>مراجعة فقط</t>
+          <t>جرد + مراجعة</t>
         </is>
       </c>
       <c r="I155" s="3" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
     </row>
     <row r="156">
@@ -6712,14 +6716,10 @@
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>د. حسام شلش</t>
-        </is>
-      </c>
-      <c r="F156" s="2" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
-      </c>
+          <t>د. علي خليفة</t>
+        </is>
+      </c>
+      <c r="F156" s="2" t="inlineStr"/>
       <c r="G156" s="2" t="inlineStr">
         <is>
           <t>نعم</t>
@@ -6727,11 +6727,11 @@
       </c>
       <c r="H156" s="2" t="inlineStr">
         <is>
-          <t>جرد + مراجعة</t>
+          <t>مراجعة فقط</t>
         </is>
       </c>
       <c r="I156" s="3" t="n">
-        <v>200</v>
+        <v>150</v>
       </c>
     </row>
     <row r="157">
@@ -6755,7 +6755,7 @@
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>د. علي خليفة</t>
+          <t>د. السيد حسن</t>
         </is>
       </c>
       <c r="F157" s="2" t="inlineStr"/>
@@ -6776,28 +6776,32 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>الأحد</t>
+          <t>الاثنين</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>الخرج</t>
+          <t>الرياض</t>
         </is>
       </c>
       <c r="D158" s="2" t="n">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>د. السيد حسن</t>
-        </is>
-      </c>
-      <c r="F158" s="2" t="inlineStr"/>
+          <t>د. علي خليفة</t>
+        </is>
+      </c>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
           <t>نعم</t>
@@ -6805,11 +6809,11 @@
       </c>
       <c r="H158" s="2" t="inlineStr">
         <is>
-          <t>مراجعة فقط</t>
+          <t>جرد + مراجعة</t>
         </is>
       </c>
       <c r="I158" s="3" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
     </row>
     <row r="159">
@@ -6833,14 +6837,10 @@
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>د. علي خليفة</t>
-        </is>
-      </c>
-      <c r="F159" s="2" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
-      </c>
+          <t>د. حسام شلش</t>
+        </is>
+      </c>
+      <c r="F159" s="2" t="inlineStr"/>
       <c r="G159" s="2" t="inlineStr">
         <is>
           <t>نعم</t>
@@ -6848,11 +6848,11 @@
       </c>
       <c r="H159" s="2" t="inlineStr">
         <is>
-          <t>جرد + مراجعة</t>
+          <t>مراجعة فقط</t>
         </is>
       </c>
       <c r="I159" s="3" t="n">
-        <v>200</v>
+        <v>150</v>
       </c>
     </row>
     <row r="160">
@@ -6876,7 +6876,7 @@
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>د. حسام شلش</t>
+          <t>د. السيد حسن</t>
         </is>
       </c>
       <c r="F160" s="2" t="inlineStr"/>
@@ -6911,14 +6911,18 @@
         </is>
       </c>
       <c r="D161" s="2" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>د. السيد حسن</t>
-        </is>
-      </c>
-      <c r="F161" s="2" t="inlineStr"/>
+          <t>د. علي خليفة</t>
+        </is>
+      </c>
+      <c r="F161" s="2" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="G161" s="2" t="inlineStr">
         <is>
           <t>نعم</t>
@@ -6926,11 +6930,11 @@
       </c>
       <c r="H161" s="2" t="inlineStr">
         <is>
-          <t>مراجعة فقط</t>
+          <t>جرد + مراجعة</t>
         </is>
       </c>
       <c r="I161" s="3" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
     </row>
     <row r="162">
@@ -6954,14 +6958,10 @@
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>د. علي خليفة</t>
-        </is>
-      </c>
-      <c r="F162" s="2" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
-      </c>
+          <t>د. حسام شلش</t>
+        </is>
+      </c>
+      <c r="F162" s="2" t="inlineStr"/>
       <c r="G162" s="2" t="inlineStr">
         <is>
           <t>نعم</t>
@@ -6969,11 +6969,11 @@
       </c>
       <c r="H162" s="2" t="inlineStr">
         <is>
-          <t>جرد + مراجعة</t>
+          <t>مراجعة فقط</t>
         </is>
       </c>
       <c r="I162" s="3" t="n">
-        <v>200</v>
+        <v>150</v>
       </c>
     </row>
     <row r="163">
@@ -6997,7 +6997,7 @@
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>د. حسام شلش</t>
+          <t>د. السيد حسن</t>
         </is>
       </c>
       <c r="F163" s="2" t="inlineStr"/>
@@ -7018,12 +7018,12 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>الاثنين</t>
+          <t>الثلاثاء</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
@@ -7032,14 +7032,18 @@
         </is>
       </c>
       <c r="D164" s="2" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>د. السيد حسن</t>
-        </is>
-      </c>
-      <c r="F164" s="2" t="inlineStr"/>
+          <t>د. حسام شلش</t>
+        </is>
+      </c>
+      <c r="F164" s="2" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
           <t>نعم</t>
@@ -7047,11 +7051,11 @@
       </c>
       <c r="H164" s="2" t="inlineStr">
         <is>
-          <t>مراجعة فقط</t>
+          <t>جرد + مراجعة</t>
         </is>
       </c>
       <c r="I164" s="3" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
     </row>
     <row r="165">
@@ -7075,14 +7079,10 @@
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>د. حسام شلش</t>
-        </is>
-      </c>
-      <c r="F165" s="2" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
-      </c>
+          <t>د. السيد حسن</t>
+        </is>
+      </c>
+      <c r="F165" s="2" t="inlineStr"/>
       <c r="G165" s="2" t="inlineStr">
         <is>
           <t>نعم</t>
@@ -7090,11 +7090,11 @@
       </c>
       <c r="H165" s="2" t="inlineStr">
         <is>
-          <t>جرد + مراجعة</t>
+          <t>مراجعة فقط</t>
         </is>
       </c>
       <c r="I165" s="3" t="n">
-        <v>200</v>
+        <v>150</v>
       </c>
     </row>
     <row r="166">
@@ -7114,14 +7114,18 @@
         </is>
       </c>
       <c r="D166" s="2" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>د. السيد حسن</t>
-        </is>
-      </c>
-      <c r="F166" s="2" t="inlineStr"/>
+          <t>د. حسام شلش</t>
+        </is>
+      </c>
+      <c r="F166" s="2" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
           <t>نعم</t>
@@ -7129,11 +7133,11 @@
       </c>
       <c r="H166" s="2" t="inlineStr">
         <is>
-          <t>مراجعة فقط</t>
+          <t>جرد + مراجعة</t>
         </is>
       </c>
       <c r="I166" s="3" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
     </row>
     <row r="167">
@@ -7157,14 +7161,10 @@
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
-          <t>د. حسام شلش</t>
-        </is>
-      </c>
-      <c r="F167" s="2" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
-      </c>
+          <t>د. السيد حسن</t>
+        </is>
+      </c>
+      <c r="F167" s="2" t="inlineStr"/>
       <c r="G167" s="2" t="inlineStr">
         <is>
           <t>نعم</t>
@@ -7172,22 +7172,22 @@
       </c>
       <c r="H167" s="2" t="inlineStr">
         <is>
-          <t>جرد + مراجعة</t>
+          <t>مراجعة فقط</t>
         </is>
       </c>
       <c r="I167" s="3" t="n">
-        <v>200</v>
+        <v>150</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>الثلاثاء</t>
+          <t>الأربعاء</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
@@ -7196,14 +7196,18 @@
         </is>
       </c>
       <c r="D168" s="2" t="n">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>د. السيد حسن</t>
-        </is>
-      </c>
-      <c r="F168" s="2" t="inlineStr"/>
+          <t>د. علي خليفة</t>
+        </is>
+      </c>
+      <c r="F168" s="2" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
           <t>نعم</t>
@@ -7211,11 +7215,11 @@
       </c>
       <c r="H168" s="2" t="inlineStr">
         <is>
-          <t>مراجعة فقط</t>
+          <t>جرد + مراجعة</t>
         </is>
       </c>
       <c r="I168" s="3" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
     </row>
     <row r="169">
@@ -7239,14 +7243,10 @@
       </c>
       <c r="E169" s="2" t="inlineStr">
         <is>
-          <t>د. علي خليفة</t>
-        </is>
-      </c>
-      <c r="F169" s="2" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
-      </c>
+          <t>د. حسام شلش</t>
+        </is>
+      </c>
+      <c r="F169" s="2" t="inlineStr"/>
       <c r="G169" s="2" t="inlineStr">
         <is>
           <t>نعم</t>
@@ -7254,11 +7254,11 @@
       </c>
       <c r="H169" s="2" t="inlineStr">
         <is>
-          <t>جرد + مراجعة</t>
+          <t>مراجعة فقط</t>
         </is>
       </c>
       <c r="I169" s="3" t="n">
-        <v>200</v>
+        <v>150</v>
       </c>
     </row>
     <row r="170">
@@ -7282,7 +7282,7 @@
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>د. حسام شلش</t>
+          <t>د. السيد حسن</t>
         </is>
       </c>
       <c r="F170" s="2" t="inlineStr"/>
@@ -7317,14 +7317,18 @@
         </is>
       </c>
       <c r="D171" s="2" t="n">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="E171" s="2" t="inlineStr">
         <is>
-          <t>د. السيد حسن</t>
-        </is>
-      </c>
-      <c r="F171" s="2" t="inlineStr"/>
+          <t>د. علي خليفة</t>
+        </is>
+      </c>
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="G171" s="2" t="inlineStr">
         <is>
           <t>نعم</t>
@@ -7332,11 +7336,11 @@
       </c>
       <c r="H171" s="2" t="inlineStr">
         <is>
-          <t>مراجعة فقط</t>
+          <t>جرد + مراجعة</t>
         </is>
       </c>
       <c r="I171" s="3" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
     </row>
     <row r="172">
@@ -7360,14 +7364,10 @@
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>د. علي خليفة</t>
-        </is>
-      </c>
-      <c r="F172" s="2" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
-      </c>
+          <t>د. حسام شلش</t>
+        </is>
+      </c>
+      <c r="F172" s="2" t="inlineStr"/>
       <c r="G172" s="2" t="inlineStr">
         <is>
           <t>نعم</t>
@@ -7375,11 +7375,11 @@
       </c>
       <c r="H172" s="2" t="inlineStr">
         <is>
-          <t>جرد + مراجعة</t>
+          <t>مراجعة فقط</t>
         </is>
       </c>
       <c r="I172" s="3" t="n">
-        <v>200</v>
+        <v>150</v>
       </c>
     </row>
     <row r="173">
@@ -7403,7 +7403,7 @@
       </c>
       <c r="E173" s="2" t="inlineStr">
         <is>
-          <t>د. حسام شلش</t>
+          <t>د. السيد حسن</t>
         </is>
       </c>
       <c r="F173" s="2" t="inlineStr"/>
@@ -7424,28 +7424,32 @@
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>الأربعاء</t>
+          <t>الخميس</t>
         </is>
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>الرياض</t>
+          <t>الخرج</t>
         </is>
       </c>
       <c r="D174" s="2" t="n">
-        <v>58</v>
+        <v>6</v>
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
-          <t>د. السيد حسن</t>
-        </is>
-      </c>
-      <c r="F174" s="2" t="inlineStr"/>
+          <t>د. حسام شلش</t>
+        </is>
+      </c>
+      <c r="F174" s="2" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="G174" s="2" t="inlineStr">
         <is>
           <t>نعم</t>
@@ -7453,11 +7457,11 @@
       </c>
       <c r="H174" s="2" t="inlineStr">
         <is>
-          <t>مراجعة فقط</t>
+          <t>جرد + مراجعة</t>
         </is>
       </c>
       <c r="I174" s="3" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
     </row>
     <row r="175">
@@ -7481,14 +7485,10 @@
       </c>
       <c r="E175" s="2" t="inlineStr">
         <is>
-          <t>د. حسام شلش</t>
-        </is>
-      </c>
-      <c r="F175" s="2" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
-      </c>
+          <t>د. علي خليفة</t>
+        </is>
+      </c>
+      <c r="F175" s="2" t="inlineStr"/>
       <c r="G175" s="2" t="inlineStr">
         <is>
           <t>نعم</t>
@@ -7496,11 +7496,11 @@
       </c>
       <c r="H175" s="2" t="inlineStr">
         <is>
-          <t>جرد + مراجعة</t>
+          <t>مراجعة فقط</t>
         </is>
       </c>
       <c r="I175" s="3" t="n">
-        <v>200</v>
+        <v>150</v>
       </c>
     </row>
     <row r="176">
@@ -7520,14 +7520,18 @@
         </is>
       </c>
       <c r="D176" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
-          <t>د. علي خليفة</t>
-        </is>
-      </c>
-      <c r="F176" s="2" t="inlineStr"/>
+          <t>د. حسام شلش</t>
+        </is>
+      </c>
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="G176" s="2" t="inlineStr">
         <is>
           <t>نعم</t>
@@ -7535,11 +7539,11 @@
       </c>
       <c r="H176" s="2" t="inlineStr">
         <is>
-          <t>مراجعة فقط</t>
+          <t>جرد + مراجعة</t>
         </is>
       </c>
       <c r="I176" s="3" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
     </row>
     <row r="177">
@@ -7563,14 +7567,10 @@
       </c>
       <c r="E177" s="2" t="inlineStr">
         <is>
-          <t>د. حسام شلش</t>
-        </is>
-      </c>
-      <c r="F177" s="2" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
-      </c>
+          <t>د. السيد حسن</t>
+        </is>
+      </c>
+      <c r="F177" s="2" t="inlineStr"/>
       <c r="G177" s="2" t="inlineStr">
         <is>
           <t>نعم</t>
@@ -7578,11 +7578,11 @@
       </c>
       <c r="H177" s="2" t="inlineStr">
         <is>
-          <t>جرد + مراجعة</t>
+          <t>مراجعة فقط</t>
         </is>
       </c>
       <c r="I177" s="3" t="n">
-        <v>200</v>
+        <v>150</v>
       </c>
     </row>
     <row r="178">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
-          <t>د. السيد حسن</t>
+          <t>د. علي خليفة</t>
         </is>
       </c>
       <c r="F178" s="2" t="inlineStr"/>
@@ -7625,64 +7625,25 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="B179" s="2" t="inlineStr">
-        <is>
-          <t>الخميس</t>
-        </is>
-      </c>
-      <c r="C179" s="2" t="inlineStr">
-        <is>
-          <t>الخرج</t>
-        </is>
-      </c>
-      <c r="D179" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="E179" s="2" t="inlineStr">
-        <is>
-          <t>د. علي خليفة</t>
-        </is>
-      </c>
-      <c r="F179" s="2" t="inlineStr"/>
-      <c r="G179" s="2" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
-      </c>
-      <c r="H179" s="2" t="inlineStr">
-        <is>
-          <t>مراجعة فقط</t>
-        </is>
-      </c>
-      <c r="I179" s="3" t="n">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" s="4" t="inlineStr">
+      <c r="A179" s="4" t="inlineStr">
         <is>
           <t>الإجمالي</t>
         </is>
       </c>
-      <c r="B180" s="4" t="n"/>
-      <c r="C180" s="4" t="n"/>
-      <c r="D180" s="4" t="n"/>
-      <c r="E180" s="4" t="n"/>
-      <c r="F180" s="4" t="n"/>
-      <c r="G180" s="4" t="n"/>
-      <c r="H180" s="4" t="n"/>
-      <c r="I180" s="5">
-        <f>SUM(I2:I179)</f>
-        <v>29000</v>
+      <c r="B179" s="4" t="n"/>
+      <c r="C179" s="4" t="n"/>
+      <c r="D179" s="4" t="n"/>
+      <c r="E179" s="4" t="n"/>
+      <c r="F179" s="4" t="n"/>
+      <c r="G179" s="4" t="n"/>
+      <c r="H179" s="4" t="n"/>
+      <c r="I179" s="5">
+        <f>SUM(I2:I178)</f>
+        <v>28850</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I179"/>
+  <autoFilter ref="A1:I178"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>